--- a/Report for school.xlsx
+++ b/Report for school.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26924"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faith\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sena Dela Cruz\Documents\_My Made Projects\Actual Senior Project\Senior-Project-F23\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB12A22-51C7-4314-B7F9-F588E93F9DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="1755" yWindow="0" windowWidth="26550" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Custom Report" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="462">
   <si>
     <t>Created On</t>
   </si>
@@ -1285,13 +1286,133 @@
   </si>
   <si>
     <t>Trenton, Trenton West side, 155</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Temperament</t>
+  </si>
+  <si>
+    <t>Personality</t>
+  </si>
+  <si>
+    <t>big</t>
+  </si>
+  <si>
+    <t>Energetic</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Playful, affectionate</t>
+  </si>
+  <si>
+    <t>playful, intelligent</t>
+  </si>
+  <si>
+    <t>active, intelligent</t>
+  </si>
+  <si>
+    <t>Playful</t>
+  </si>
+  <si>
+    <t>friendly, confident</t>
+  </si>
+  <si>
+    <t>intelligent, playful</t>
+  </si>
+  <si>
+    <t>friendly, energetic</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>friendly, intelligent</t>
+  </si>
+  <si>
+    <t>Protective</t>
+  </si>
+  <si>
+    <t>Intelligent, Independent</t>
+  </si>
+  <si>
+    <t>small</t>
+  </si>
+  <si>
+    <t>friendly</t>
+  </si>
+  <si>
+    <t>Intelligent</t>
+  </si>
+  <si>
+    <t>active, independent</t>
+  </si>
+  <si>
+    <t>active, protective</t>
+  </si>
+  <si>
+    <t>friendly, outgoing</t>
+  </si>
+  <si>
+    <t>Playful, curious</t>
+  </si>
+  <si>
+    <t>alert, fearless</t>
+  </si>
+  <si>
+    <t>intelligent, independent</t>
+  </si>
+  <si>
+    <t>active, friendly</t>
+  </si>
+  <si>
+    <t>friendly, social</t>
+  </si>
+  <si>
+    <t>protective, loyal</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>intelligent, obedient</t>
+  </si>
+  <si>
+    <t>playful, active</t>
+  </si>
+  <si>
+    <t>friendly, independent</t>
+  </si>
+  <si>
+    <t>friendly, active</t>
+  </si>
+  <si>
+    <t>intelligent, protective</t>
+  </si>
+  <si>
+    <t>loyal, protective</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>playful, outgoing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1302,6 +1423,13 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1324,9 +1452,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1345,9 +1474,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1385,7 +1514,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1457,7 +1586,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1630,24 +1759,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K89"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O89"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="51.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="51.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,8 +1812,17 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M1" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1713,8 +1853,17 @@
       <c r="K2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M2" t="s">
+        <v>425</v>
+      </c>
+      <c r="N2" t="s">
+        <v>426</v>
+      </c>
+      <c r="O2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1745,8 +1894,17 @@
       <c r="K3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M3" t="s">
+        <v>428</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
@@ -1777,8 +1935,17 @@
       <c r="K4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N4" t="s">
+        <v>429</v>
+      </c>
+      <c r="O4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
@@ -1812,8 +1979,17 @@
       <c r="K5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M5" t="s">
+        <v>425</v>
+      </c>
+      <c r="N5" t="s">
+        <v>426</v>
+      </c>
+      <c r="O5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1844,8 +2020,17 @@
       <c r="K6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>428</v>
+      </c>
+      <c r="N6" t="s">
+        <v>429</v>
+      </c>
+      <c r="O6" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -1879,8 +2064,17 @@
       <c r="K7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>428</v>
+      </c>
+      <c r="N7" t="s">
+        <v>429</v>
+      </c>
+      <c r="O7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -1911,8 +2105,17 @@
       <c r="K8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M8" t="s">
+        <v>428</v>
+      </c>
+      <c r="N8" t="s">
+        <v>433</v>
+      </c>
+      <c r="O8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -1946,8 +2149,17 @@
       <c r="K9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M9" t="s">
+        <v>428</v>
+      </c>
+      <c r="N9" t="s">
+        <v>429</v>
+      </c>
+      <c r="O9" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1978,8 +2190,17 @@
       <c r="K10" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>428</v>
+      </c>
+      <c r="N10" t="s">
+        <v>429</v>
+      </c>
+      <c r="O10" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -2010,8 +2231,17 @@
       <c r="K11" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M11" t="s">
+        <v>425</v>
+      </c>
+      <c r="N11" t="s">
+        <v>426</v>
+      </c>
+      <c r="O11" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>74</v>
       </c>
@@ -2042,8 +2272,17 @@
       <c r="K12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M12" t="s">
+        <v>428</v>
+      </c>
+      <c r="N12" t="s">
+        <v>433</v>
+      </c>
+      <c r="O12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>80</v>
       </c>
@@ -2074,8 +2313,17 @@
       <c r="K13" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M13" t="s">
+        <v>425</v>
+      </c>
+      <c r="N13" t="s">
+        <v>437</v>
+      </c>
+      <c r="O13" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -2106,8 +2354,17 @@
       <c r="K14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M14" t="s">
+        <v>428</v>
+      </c>
+      <c r="N14" t="s">
+        <v>433</v>
+      </c>
+      <c r="O14" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>89</v>
       </c>
@@ -2141,8 +2398,17 @@
       <c r="K15" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>425</v>
+      </c>
+      <c r="N15" t="s">
+        <v>426</v>
+      </c>
+      <c r="O15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2173,8 +2439,17 @@
       <c r="K16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M16" t="s">
+        <v>425</v>
+      </c>
+      <c r="N16" t="s">
+        <v>439</v>
+      </c>
+      <c r="O16" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>94</v>
       </c>
@@ -2205,8 +2480,17 @@
       <c r="K17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>428</v>
+      </c>
+      <c r="N17" t="s">
+        <v>429</v>
+      </c>
+      <c r="O17" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>102</v>
       </c>
@@ -2240,8 +2524,17 @@
       <c r="K18" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M18" t="s">
+        <v>441</v>
+      </c>
+      <c r="N18" t="s">
+        <v>433</v>
+      </c>
+      <c r="O18" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>108</v>
       </c>
@@ -2269,8 +2562,17 @@
       <c r="K19" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M19" t="s">
+        <v>441</v>
+      </c>
+      <c r="N19" t="s">
+        <v>433</v>
+      </c>
+      <c r="O19" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>113</v>
       </c>
@@ -2304,8 +2606,17 @@
       <c r="K20" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M20" t="s">
+        <v>428</v>
+      </c>
+      <c r="N20" t="s">
+        <v>443</v>
+      </c>
+      <c r="O20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>118</v>
       </c>
@@ -2336,8 +2647,17 @@
       <c r="K21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M21" t="s">
+        <v>428</v>
+      </c>
+      <c r="N21" t="s">
+        <v>443</v>
+      </c>
+      <c r="O21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
@@ -2371,8 +2691,17 @@
       <c r="K22" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M22" t="s">
+        <v>428</v>
+      </c>
+      <c r="N22" t="s">
+        <v>437</v>
+      </c>
+      <c r="O22" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -2403,8 +2732,17 @@
       <c r="K23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M23" t="s">
+        <v>425</v>
+      </c>
+      <c r="N23" t="s">
+        <v>437</v>
+      </c>
+      <c r="O23" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>129</v>
       </c>
@@ -2435,8 +2773,17 @@
       <c r="K24" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M24" t="s">
+        <v>425</v>
+      </c>
+      <c r="N24" t="s">
+        <v>437</v>
+      </c>
+      <c r="O24" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -2470,8 +2817,17 @@
       <c r="K25" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M25" t="s">
+        <v>428</v>
+      </c>
+      <c r="N25" t="s">
+        <v>443</v>
+      </c>
+      <c r="O25" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>137</v>
       </c>
@@ -2505,8 +2861,17 @@
       <c r="K26" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M26" t="s">
+        <v>428</v>
+      </c>
+      <c r="N26" t="s">
+        <v>443</v>
+      </c>
+      <c r="O26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>146</v>
       </c>
@@ -2540,8 +2905,17 @@
       <c r="K27" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M27" t="s">
+        <v>428</v>
+      </c>
+      <c r="N27" t="s">
+        <v>433</v>
+      </c>
+      <c r="O27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>151</v>
       </c>
@@ -2572,8 +2946,17 @@
       <c r="K28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M28" t="s">
+        <v>428</v>
+      </c>
+      <c r="N28" t="s">
+        <v>426</v>
+      </c>
+      <c r="O28" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>151</v>
       </c>
@@ -2607,8 +2990,17 @@
       <c r="K29" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M29" t="s">
+        <v>428</v>
+      </c>
+      <c r="N29" t="s">
+        <v>429</v>
+      </c>
+      <c r="O29" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>151</v>
       </c>
@@ -2642,8 +3034,17 @@
       <c r="K30" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M30" t="s">
+        <v>428</v>
+      </c>
+      <c r="N30" t="s">
+        <v>429</v>
+      </c>
+      <c r="O30" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>164</v>
       </c>
@@ -2677,8 +3078,17 @@
       <c r="K31" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M31" t="s">
+        <v>428</v>
+      </c>
+      <c r="N31" t="s">
+        <v>437</v>
+      </c>
+      <c r="O31" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>164</v>
       </c>
@@ -2709,8 +3119,17 @@
       <c r="K32" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M32" t="s">
+        <v>428</v>
+      </c>
+      <c r="N32" t="s">
+        <v>437</v>
+      </c>
+      <c r="O32" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>173</v>
       </c>
@@ -2744,8 +3163,17 @@
       <c r="K33" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M33" t="s">
+        <v>425</v>
+      </c>
+      <c r="N33" t="s">
+        <v>426</v>
+      </c>
+      <c r="O33" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>178</v>
       </c>
@@ -2779,8 +3207,17 @@
       <c r="K34" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M34" t="s">
+        <v>428</v>
+      </c>
+      <c r="N34" t="s">
+        <v>433</v>
+      </c>
+      <c r="O34" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>183</v>
       </c>
@@ -2814,8 +3251,17 @@
       <c r="K35" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M35" t="s">
+        <v>425</v>
+      </c>
+      <c r="N35" t="s">
+        <v>426</v>
+      </c>
+      <c r="O35" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>188</v>
       </c>
@@ -2846,8 +3292,17 @@
       <c r="K36" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M36" t="s">
+        <v>428</v>
+      </c>
+      <c r="N36" t="s">
+        <v>433</v>
+      </c>
+      <c r="O36" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>193</v>
       </c>
@@ -2881,8 +3336,17 @@
       <c r="K37" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M37" t="s">
+        <v>425</v>
+      </c>
+      <c r="N37" t="s">
+        <v>437</v>
+      </c>
+      <c r="O37" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>198</v>
       </c>
@@ -2913,8 +3377,17 @@
       <c r="K38" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M38" t="s">
+        <v>441</v>
+      </c>
+      <c r="N38" t="s">
+        <v>429</v>
+      </c>
+      <c r="O38" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>203</v>
       </c>
@@ -2945,8 +3418,17 @@
       <c r="K39" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M39" t="s">
+        <v>428</v>
+      </c>
+      <c r="N39" t="s">
+        <v>429</v>
+      </c>
+      <c r="O39" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>203</v>
       </c>
@@ -2977,8 +3459,17 @@
       <c r="K40" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M40" t="s">
+        <v>428</v>
+      </c>
+      <c r="N40" t="s">
+        <v>437</v>
+      </c>
+      <c r="O40" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -3012,8 +3503,17 @@
       <c r="K41" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M41" t="s">
+        <v>428</v>
+      </c>
+      <c r="N41" t="s">
+        <v>433</v>
+      </c>
+      <c r="O41" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>214</v>
       </c>
@@ -3047,8 +3547,17 @@
       <c r="K42" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M42" t="s">
+        <v>425</v>
+      </c>
+      <c r="N42" t="s">
+        <v>426</v>
+      </c>
+      <c r="O42" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>214</v>
       </c>
@@ -3082,8 +3591,17 @@
       <c r="K43" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M43" t="s">
+        <v>425</v>
+      </c>
+      <c r="N43" t="s">
+        <v>426</v>
+      </c>
+      <c r="O43" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>222</v>
       </c>
@@ -3114,8 +3632,17 @@
       <c r="K44" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M44" t="s">
+        <v>425</v>
+      </c>
+      <c r="N44" t="s">
+        <v>437</v>
+      </c>
+      <c r="O44" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>227</v>
       </c>
@@ -3149,8 +3676,17 @@
       <c r="K45" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M45" t="s">
+        <v>428</v>
+      </c>
+      <c r="N45" t="s">
+        <v>437</v>
+      </c>
+      <c r="O45" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>227</v>
       </c>
@@ -3184,8 +3720,17 @@
       <c r="K46" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M46" t="s">
+        <v>425</v>
+      </c>
+      <c r="N46" t="s">
+        <v>437</v>
+      </c>
+      <c r="O46" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>236</v>
       </c>
@@ -3216,8 +3761,17 @@
       <c r="K47" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M47" t="s">
+        <v>425</v>
+      </c>
+      <c r="N47" t="s">
+        <v>437</v>
+      </c>
+      <c r="O47" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>241</v>
       </c>
@@ -3248,8 +3802,17 @@
       <c r="K48" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M48" t="s">
+        <v>428</v>
+      </c>
+      <c r="N48" t="s">
+        <v>437</v>
+      </c>
+      <c r="O48" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>241</v>
       </c>
@@ -3283,8 +3846,17 @@
       <c r="K49" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M49" t="s">
+        <v>428</v>
+      </c>
+      <c r="N49" t="s">
+        <v>443</v>
+      </c>
+      <c r="O49" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>241</v>
       </c>
@@ -3318,8 +3890,17 @@
       <c r="K50" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M50" t="s">
+        <v>425</v>
+      </c>
+      <c r="N50" t="s">
+        <v>426</v>
+      </c>
+      <c r="O50" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>252</v>
       </c>
@@ -3353,8 +3934,17 @@
       <c r="K51" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M51" t="s">
+        <v>425</v>
+      </c>
+      <c r="N51" t="s">
+        <v>439</v>
+      </c>
+      <c r="O51" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>258</v>
       </c>
@@ -3388,8 +3978,17 @@
       <c r="K52" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M52" t="s">
+        <v>428</v>
+      </c>
+      <c r="N52" t="s">
+        <v>443</v>
+      </c>
+      <c r="O52" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>258</v>
       </c>
@@ -3423,8 +4022,17 @@
       <c r="K53" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M53" t="s">
+        <v>425</v>
+      </c>
+      <c r="N53" t="s">
+        <v>437</v>
+      </c>
+      <c r="O53" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>258</v>
       </c>
@@ -3458,8 +4066,17 @@
       <c r="K54" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M54" t="s">
+        <v>428</v>
+      </c>
+      <c r="N54" t="s">
+        <v>433</v>
+      </c>
+      <c r="O54" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>272</v>
       </c>
@@ -3490,8 +4107,17 @@
       <c r="K55" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M55" t="s">
+        <v>428</v>
+      </c>
+      <c r="N55" t="s">
+        <v>437</v>
+      </c>
+      <c r="O55" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>276</v>
       </c>
@@ -3525,8 +4151,17 @@
       <c r="K56" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M56" t="s">
+        <v>428</v>
+      </c>
+      <c r="N56" t="s">
+        <v>443</v>
+      </c>
+      <c r="O56" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>276</v>
       </c>
@@ -3560,8 +4195,17 @@
       <c r="K57" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M57" t="s">
+        <v>428</v>
+      </c>
+      <c r="N57" t="s">
+        <v>453</v>
+      </c>
+      <c r="O57" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>276</v>
       </c>
@@ -3595,8 +4239,17 @@
       <c r="K58" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M58" t="s">
+        <v>425</v>
+      </c>
+      <c r="N58" t="s">
+        <v>426</v>
+      </c>
+      <c r="O58" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>276</v>
       </c>
@@ -3630,8 +4283,17 @@
       <c r="K59" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M59" t="s">
+        <v>441</v>
+      </c>
+      <c r="N59" t="s">
+        <v>433</v>
+      </c>
+      <c r="O59" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>290</v>
       </c>
@@ -3662,8 +4324,17 @@
       <c r="K60" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M60" t="s">
+        <v>425</v>
+      </c>
+      <c r="N60" t="s">
+        <v>437</v>
+      </c>
+      <c r="O60" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>290</v>
       </c>
@@ -3694,8 +4365,17 @@
       <c r="K61" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M61" t="s">
+        <v>428</v>
+      </c>
+      <c r="N61" t="s">
+        <v>429</v>
+      </c>
+      <c r="O61" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>290</v>
       </c>
@@ -3729,8 +4409,17 @@
       <c r="K62" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M62" t="s">
+        <v>428</v>
+      </c>
+      <c r="N62" t="s">
+        <v>433</v>
+      </c>
+      <c r="O62" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>302</v>
       </c>
@@ -3764,8 +4453,17 @@
       <c r="K63" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M63" t="s">
+        <v>428</v>
+      </c>
+      <c r="N63" t="s">
+        <v>429</v>
+      </c>
+      <c r="O63" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>302</v>
       </c>
@@ -3796,8 +4494,17 @@
       <c r="K64" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M64" t="s">
+        <v>425</v>
+      </c>
+      <c r="N64" t="s">
+        <v>426</v>
+      </c>
+      <c r="O64" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>312</v>
       </c>
@@ -3831,8 +4538,17 @@
       <c r="K65" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M65" t="s">
+        <v>428</v>
+      </c>
+      <c r="N65" t="s">
+        <v>433</v>
+      </c>
+      <c r="O65" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>312</v>
       </c>
@@ -3866,8 +4582,17 @@
       <c r="K66" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M66" t="s">
+        <v>428</v>
+      </c>
+      <c r="N66" t="s">
+        <v>29</v>
+      </c>
+      <c r="O66" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>320</v>
       </c>
@@ -3898,8 +4623,17 @@
       <c r="K67" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M67" t="s">
+        <v>428</v>
+      </c>
+      <c r="N67" t="s">
+        <v>439</v>
+      </c>
+      <c r="O67" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>326</v>
       </c>
@@ -3930,8 +4664,17 @@
       <c r="K68" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M68" t="s">
+        <v>428</v>
+      </c>
+      <c r="N68" t="s">
+        <v>429</v>
+      </c>
+      <c r="O68" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>331</v>
       </c>
@@ -3965,8 +4708,17 @@
       <c r="K69" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M69" t="s">
+        <v>428</v>
+      </c>
+      <c r="N69" t="s">
+        <v>429</v>
+      </c>
+      <c r="O69" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>336</v>
       </c>
@@ -4000,8 +4752,17 @@
       <c r="K70" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M70" t="s">
+        <v>425</v>
+      </c>
+      <c r="N70" t="s">
+        <v>426</v>
+      </c>
+      <c r="O70" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>341</v>
       </c>
@@ -4032,8 +4793,17 @@
       <c r="K71" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M71" t="s">
+        <v>428</v>
+      </c>
+      <c r="N71" t="s">
+        <v>433</v>
+      </c>
+      <c r="O71" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>346</v>
       </c>
@@ -4067,8 +4837,17 @@
       <c r="K72" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M72" t="s">
+        <v>425</v>
+      </c>
+      <c r="N72" t="s">
+        <v>443</v>
+      </c>
+      <c r="O72" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>351</v>
       </c>
@@ -4102,8 +4881,17 @@
       <c r="K73" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M73" t="s">
+        <v>428</v>
+      </c>
+      <c r="N73" t="s">
+        <v>433</v>
+      </c>
+      <c r="O73" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>356</v>
       </c>
@@ -4134,8 +4922,17 @@
       <c r="K74" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M74" t="s">
+        <v>428</v>
+      </c>
+      <c r="N74" t="s">
+        <v>433</v>
+      </c>
+      <c r="O74" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>360</v>
       </c>
@@ -4169,8 +4966,17 @@
       <c r="K75" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M75" t="s">
+        <v>428</v>
+      </c>
+      <c r="N75" t="s">
+        <v>29</v>
+      </c>
+      <c r="O75" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>365</v>
       </c>
@@ -4201,8 +5007,17 @@
       <c r="K76" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M76" t="s">
+        <v>425</v>
+      </c>
+      <c r="N76" t="s">
+        <v>437</v>
+      </c>
+      <c r="O76" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>369</v>
       </c>
@@ -4236,8 +5051,17 @@
       <c r="K77" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M77" t="s">
+        <v>428</v>
+      </c>
+      <c r="N77" t="s">
+        <v>429</v>
+      </c>
+      <c r="O77" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>374</v>
       </c>
@@ -4271,8 +5095,17 @@
       <c r="K78" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M78" t="s">
+        <v>428</v>
+      </c>
+      <c r="N78" t="s">
+        <v>460</v>
+      </c>
+      <c r="O78" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>374</v>
       </c>
@@ -4303,8 +5136,17 @@
       <c r="K79" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M79" t="s">
+        <v>425</v>
+      </c>
+      <c r="N79" t="s">
+        <v>437</v>
+      </c>
+      <c r="O79" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>374</v>
       </c>
@@ -4335,8 +5177,17 @@
       <c r="K80" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M80" t="s">
+        <v>428</v>
+      </c>
+      <c r="N80" t="s">
+        <v>437</v>
+      </c>
+      <c r="O80" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>374</v>
       </c>
@@ -4367,8 +5218,17 @@
       <c r="K81" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M81" t="s">
+        <v>425</v>
+      </c>
+      <c r="N81" t="s">
+        <v>426</v>
+      </c>
+      <c r="O81" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>387</v>
       </c>
@@ -4399,8 +5259,17 @@
       <c r="K82" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M82" t="s">
+        <v>425</v>
+      </c>
+      <c r="N82" t="s">
+        <v>437</v>
+      </c>
+      <c r="O82" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>391</v>
       </c>
@@ -4428,8 +5297,17 @@
       <c r="K83" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M83" t="s">
+        <v>428</v>
+      </c>
+      <c r="N83" t="s">
+        <v>433</v>
+      </c>
+      <c r="O83" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>395</v>
       </c>
@@ -4463,8 +5341,17 @@
       <c r="K84" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M84" t="s">
+        <v>441</v>
+      </c>
+      <c r="N84" t="s">
+        <v>426</v>
+      </c>
+      <c r="O84" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>399</v>
       </c>
@@ -4498,8 +5385,17 @@
       <c r="K85" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M85" t="s">
+        <v>428</v>
+      </c>
+      <c r="N85" t="s">
+        <v>429</v>
+      </c>
+      <c r="O85" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>399</v>
       </c>
@@ -4533,8 +5429,17 @@
       <c r="K86" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M86" t="s">
+        <v>425</v>
+      </c>
+      <c r="N86" t="s">
+        <v>443</v>
+      </c>
+      <c r="O86" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>399</v>
       </c>
@@ -4565,8 +5470,17 @@
       <c r="K87" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M87" t="s">
+        <v>428</v>
+      </c>
+      <c r="N87" t="s">
+        <v>429</v>
+      </c>
+      <c r="O87" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>412</v>
       </c>
@@ -4600,8 +5514,17 @@
       <c r="K88" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="M88" t="s">
+        <v>428</v>
+      </c>
+      <c r="N88" t="s">
+        <v>429</v>
+      </c>
+      <c r="O88" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>417</v>
       </c>
@@ -4631,6 +5554,15 @@
       </c>
       <c r="K89" t="s">
         <v>41</v>
+      </c>
+      <c r="M89" t="s">
+        <v>428</v>
+      </c>
+      <c r="N89" t="s">
+        <v>437</v>
+      </c>
+      <c r="O89" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
